--- a/cuadros/JUNIO/SANTA RITA.xlsx
+++ b/cuadros/JUNIO/SANTA RITA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,11 +524,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Proveedor paga leches por venir muy golpeadas</t>
@@ -555,6 +550,76 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260604160304</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ALIMENTOS POLAR COMERCIAL C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7242119117</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proveedor paga mantequillas por llegar sin tapas </t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>INC_091831_0.jpeg INC_091831_1.jpeg</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ID_20260605091831</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/SANTA RITA.xlsx
+++ b/cuadros/JUNIO/SANTA RITA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,11 +589,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">Proveedor paga mantequillas por llegar sin tapas </t>
@@ -620,6 +615,82 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260605091831</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7280</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ANDRES E. SALAS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Incidencia: se recibe a las 02:03pm Cava Luxor con los siguientes productos:
+•	Alcohol antiséptico el guardián 120ml
+•	Alcohol antiséptico e/guardián c/ato 120
+•	Agua oxigenada el guardián vol. 10 120ml
+•	Alcohol antiséptico el guardián 500ml
+•	Alcohol antiséptico el guardián 1LT
+•	Alcohol antiséptico el guardián 240ml</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>INC_101353_0.jpeg INC_101353_1.png INC_101353_2.png</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ID_20260608101353</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/SANTA RITA.xlsx
+++ b/cuadros/JUNIO/SANTA RITA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,6 +694,76 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SANTA RITA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>YEFFERSON MAY MORGADO CHACON</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>126684</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ANDRES E. SALAS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>se recibe a las 3:43pm Jefferson Morgado un total de 203.4kg de papaya en cual no se documentó y se elimina recepción</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>INC_101527_0.png INC_101527_1.png INC_101527_2.png INC_101527_3.png</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ID_20260608101527</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
